--- a/PCB/solar-glow-drh-v2_1-BOM.xlsx
+++ b/PCB/solar-glow-drh-v2_1-BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="190">
   <si>
     <t xml:space="preserve">Ref(s)</t>
   </si>
@@ -226,25 +226,25 @@
     <t xml:space="preserve">LED ballast — one per LED; sets per-LED current (low-side PWM)</t>
   </si>
   <si>
-    <t xml:space="preserve">150 Ω, ±1%, 25 ppm/°C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vishay Dale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TNPW1206150RFEEA</t>
+    <t xml:space="preserve">150 Ω, ±1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yageo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC0402FR-07150RL</t>
   </si>
   <si>
     <t xml:space="preserve">SIZED</t>
   </si>
   <si>
-    <t xml:space="preserve">Sized for the clamped ~3.47 V rail (~9 mA/LED peak); PWM trims the average below that. Re-tune after the energy-budget bench test.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tnpw_e3.pdf</t>
+    <t xml:space="preserve">Package corrected to 0402 to match the placed land (BOM previously listed 1206; a 1206 part will not fit). 1/16 W is ample (~12 mW peak/LED). Value still SIZED for the clamped ~3.47 V rail (~9 mA/LED peak); re-tune after the energy-budget bench test. Any 0402 150 Ω 1% equivalent works (esp. for PCBA sourcing).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
   </si>
   <si>
     <t xml:space="preserve">R12</t>
@@ -259,16 +259,10 @@
     <t xml:space="preserve">0805</t>
   </si>
   <si>
-    <t xml:space="preserve">Yageo</t>
-  </si>
-  <si>
     <t xml:space="preserve">RC0805FR-07220RL</t>
   </si>
   <si>
     <t xml:space="preserve">Sets the SW2 TINY dim level; tunable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
   </si>
   <si>
     <t xml:space="preserve">R5, R6</t>
@@ -717,8 +711,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -746,7 +744,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1009,1330 +1007,1330 @@
   <dimension ref="A1:M34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="6" t="n">
         <v>1.52</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="6" t="n">
         <f aca="false">B2*H2</f>
         <v>1.52</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="J2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="6" t="n">
         <v>6.98</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="6" t="n">
         <f aca="false">B3*H3</f>
         <v>13.96</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="4" t="s">
+      <c r="J3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="6" t="n">
         <v>0.125</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="6" t="n">
         <f aca="false">B4*H4</f>
         <v>0.25</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="4" t="s">
+      <c r="J4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="6" t="n">
         <v>15.48</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="6" t="n">
         <f aca="false">B5*H5</f>
         <v>61.92</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="4" t="s">
+      <c r="J5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="6" t="n">
         <v>7.68</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="6" t="n">
         <f aca="false">B6*H6</f>
         <v>7.68</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="4" t="s">
+      <c r="J6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="6" t="n">
         <v>0.273</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="6" t="n">
         <f aca="false">B7*H7</f>
         <v>1.092</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="4" t="s">
+      <c r="J7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="5" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="I8" s="5" t="n">
+      <c r="H8" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="6" t="n">
         <f aca="false">B8*H8</f>
-        <v>1.464</v>
-      </c>
-      <c r="J8" s="2" t="s">
+        <v>0.4</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M8" s="2" t="s">
+      <c r="L8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="6" t="n">
         <f aca="false">B9*H9</f>
         <v>0.1</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="4" t="s">
+      <c r="J9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="B10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="M9" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="E10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I10" s="6" t="n">
         <f aca="false">B10*H10</f>
         <v>0.2</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" s="4" t="s">
+      <c r="J10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="E11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="I11" s="6" t="n">
         <f aca="false">B11*H11</f>
         <v>0.05</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="4" t="s">
+      <c r="J11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="B12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="M11" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I12" s="6" t="n">
         <f aca="false">B12*H12</f>
         <v>2.5</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" s="4" t="s">
+      <c r="J12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="B13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="M12" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="E13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="I13" s="5" t="n">
+      <c r="I13" s="6" t="n">
         <f aca="false">B13*H13</f>
         <v>0.2</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="4" t="s">
+      <c r="J13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="6" t="n">
         <f aca="false">B14*H14</f>
         <v>0.4</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="4" t="s">
+      <c r="J14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="B15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="F15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="6" t="n">
         <v>0.45</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="I15" s="6" t="n">
         <f aca="false">B15*H15</f>
         <v>0.45</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K15" s="4" t="s">
+      <c r="J15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="B16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M15" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="E16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="I16" s="6" t="n">
         <f aca="false">B16*H16</f>
         <v>0.1</v>
       </c>
-      <c r="J16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="4" t="s">
+      <c r="J16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" s="4" t="s">
+      <c r="D17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H17" s="5" t="n">
+      <c r="F17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H17" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="I17" s="6" t="n">
         <f aca="false">B17*H17</f>
         <v>0.1</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K17" s="4" t="s">
+      <c r="J17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="L17" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="E18" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H18" s="5" t="n">
+      <c r="H18" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="I18" s="6" t="n">
         <f aca="false">B18*H18</f>
         <v>0.1</v>
       </c>
-      <c r="J18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="4" t="s">
+      <c r="J18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="L18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="E19" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H19" s="5" t="n">
+      <c r="H19" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="I19" s="6" t="n">
         <f aca="false">B19*H19</f>
         <v>0.09</v>
       </c>
-      <c r="J19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M19" s="2" t="s">
+      <c r="J19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="5"/>
+      <c r="L19" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E20" s="4" t="s">
+      <c r="D20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H20" s="5" t="n">
+      <c r="F20" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H20" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="I20" s="5" t="n">
+      <c r="I20" s="6" t="n">
         <f aca="false">B20*H20</f>
         <v>0.18</v>
       </c>
-      <c r="J20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K20" s="4"/>
-      <c r="L20" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="J20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="5"/>
+      <c r="L20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="E21" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H21" s="5" t="n">
+      <c r="H21" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="I21" s="5" t="n">
+      <c r="I21" s="6" t="n">
         <f aca="false">B21*H21</f>
         <v>0.04</v>
       </c>
-      <c r="J21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K21" s="4"/>
-      <c r="L21" s="2" t="s">
+      <c r="J21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K21" s="5"/>
+      <c r="L21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="M21" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="D22" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H22" s="5" t="n">
+      <c r="F22" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H22" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="I22" s="6" t="n">
         <f aca="false">B22*H22</f>
         <v>0.09</v>
       </c>
-      <c r="J22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K22" s="4"/>
-      <c r="L22" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B23" s="3" t="n">
+      <c r="J22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="5"/>
+      <c r="L22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E23" s="4" t="s">
+      <c r="C23" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H23" s="5" t="n">
+      <c r="F23" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H23" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="I23" s="5" t="n">
+      <c r="I23" s="6" t="n">
         <f aca="false">B23*H23</f>
         <v>0.09</v>
       </c>
-      <c r="J23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K23" s="4"/>
-      <c r="L23" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+      <c r="J23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" s="5"/>
+      <c r="L23" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="E24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H24" s="5" t="n">
+      <c r="H24" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="I24" s="5" t="n">
+      <c r="I24" s="6" t="n">
         <f aca="false">B24*H24</f>
         <v>0.05</v>
       </c>
-      <c r="J24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K24" s="4"/>
-      <c r="L24" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M24" s="2" t="s">
+      <c r="J24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" s="5"/>
+      <c r="L24" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M24" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="E25" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="F25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H25" s="5" t="n">
+      <c r="H25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="5" t="n">
+      <c r="I25" s="6" t="n">
         <f aca="false">B25*H25</f>
         <v>0</v>
       </c>
-      <c r="J25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K25" s="4" t="s">
+      <c r="J25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="L25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H26" s="5" t="n">
+      <c r="D26" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="5" t="n">
+      <c r="I26" s="6" t="n">
         <f aca="false">B26*H26</f>
         <v>0</v>
       </c>
-      <c r="J26" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K26" s="4" t="s">
+      <c r="J26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="L26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="D27" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="s">
+      <c r="E27" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="F27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="H27" s="5" t="n">
+      <c r="H27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="5" t="n">
+      <c r="I27" s="6" t="n">
         <f aca="false">B27*H27</f>
         <v>0</v>
       </c>
-      <c r="J27" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K27" s="4" t="s">
+      <c r="J27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="L27" s="2" t="s">
+      <c r="B28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="M27" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="D28" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="4" t="s">
+      <c r="E28" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="F28" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="H28" s="5" t="n">
+      <c r="H28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="5" t="n">
+      <c r="I28" s="6" t="n">
         <f aca="false">B28*H28</f>
         <v>0</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="J28" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="B29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="L28" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="H29" s="5" t="n">
+      <c r="H29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="I29" s="6" t="n">
         <f aca="false">B29*H29</f>
         <v>0</v>
       </c>
-      <c r="J29" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="K29" s="4"/>
-      <c r="L29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="J29" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K29" s="5"/>
+      <c r="L29" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="H30" s="5" t="n">
+      <c r="E30" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="5" t="n">
+      <c r="I30" s="6" t="n">
         <f aca="false">B30*H30</f>
         <v>0</v>
       </c>
-      <c r="J30" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="K30" s="4"/>
-      <c r="L30" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="J30" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K30" s="5"/>
+      <c r="L30" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B31" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" s="4" t="s">
+      <c r="E31" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="F31" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H31" s="5" t="n">
+      <c r="H31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="5" t="n">
+      <c r="I31" s="6" t="n">
         <f aca="false">B31*H31</f>
         <v>0</v>
       </c>
-      <c r="J31" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K31" s="4" t="s">
+      <c r="J31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G32" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <f aca="false">SUM(I2:I31)</f>
+        <v>91.562</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="L31" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G32" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="I32" s="7" t="n">
-        <f aca="false">SUM(I2:I31)</f>
-        <v>92.626</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
